--- a/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa aide maman dans la cuisine. Elles préparent une soupe chaude. Soudain, le couvercle saute. Un nuage de vapeur sort. Léa sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Léa dit : je suis surprise. Maman dit : d'abord respirer. Ensuite comprendre, avant d'agir. Léa souffle une grande fois. Elle regarde le faitout. Elle dit : je veux comprendre. Elle voit la vapeur. Elle dit : c'est chaud, c'est la soupe. Rien n'est cassé. Maman baisse le feu. Elles continuent ensemble. Être surpris, on peut respirer. Puis on cherche à comprendre.</t>
+          <t>Léa aide maman dans la cuisine. Elles préparent une soupe chaude. Soudain, le couvercle saute. Un nuage de vapeur sort. Léa sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Je suis surprise. D'abord respirer. Ensuite comprendre, avant d'agir. Léa souffle une grande fois. Elle regarde le faitout. Je veux comprendre. Elle voit la vapeur. C'est chaud, c'est la soupe. Rien n'est cassé. Maman baisse le feu. Elles continuent ensemble. Être surpris, on peut respirer. Puis on cherche à comprendre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa aide maman dans la cuisine. Elles préparent une soupe chaude. Soudain, le couvercle saute. Un nuage de vapeur sort. Léa sent son cœur battre vite. Ses yeux s'ouvrent tout grands.
+enfant-f|Je suis surprise.
+maman|D'abord respirer. Ensuite comprendre, avant d'agir.
+narrateur|Léa souffle une grande fois. Elle regarde le faitout.
+narrateur|Je veux comprendre. Elle voit la vapeur.
+narrateur|C'est chaud, c'est la soupe. Rien n'est cassé. Maman baisse le feu. Elles continuent ensemble. Être surpris, on peut respirer.
+narrateur|Puis on cherche à comprendre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a nommé : surpris. Elle a soufflé. Elle a voulu comprendre avant d'agir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La soupe mijote tout doucement. Léa pose la cuillère. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Puis on cherche à comprendre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Léa est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Léa a nommé : surpris. Elle a soufflé. Elle a voulu comprendre avant d'agir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|La soupe mijote tout doucement. Léa pose la cuillère. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Être surpris</t>
+          <t>La soupe de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le couvercle saute. Chouchou est surpris. Il souffle. Il regarde. Il comprend : c'est la soupe.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa aide maman dans la cuisine. Elles préparent une soupe chaude. Soudain, le couvercle saute. Un nuage de vapeur sort. Léa sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Je suis surprise. D'abord respirer. Ensuite comprendre, avant d'agir. Léa souffle une grande fois. Elle regarde le faitout. Je veux comprendre. Elle voit la vapeur. C'est chaud, c'est la soupe. Rien n'est cassé. Maman baisse le feu. Elles continuent ensemble. Être surpris, on peut respirer. Puis on cherche à comprendre.</t>
+          <t>Des peaux de carotte attendent. Elles sont orange et un peu humides. Une cuillère en bois repose. Le bois sent le chaud. La vitre de la cuisine est embuée. La soupe a fait un nuage doux. Le couvercle fait un petit tic. Tic, puis encore tic. Une branche de thym sent fort. Tu as entendu, Chouchou ? Ça tic. C'est le couvercle. La soupe est avec nous. Tu sens le thym ? Ça pique un peu. En ce moment, Chouchou tient la table. Le bois est un peu collant. Tu me passes le sel ? Oui, maman. Soudain, le couvercle saute. Un nuage de vapeur sort. Ça fait un souffle chaud. Chouchou sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Je suis surpris. Tu es surpris. Ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Chouchou souffle une grande fois. Ses épaules redescendent. Tu veux comprendre ? Je veux comprendre. Il regarde le faitout, de loin. La vapeur monte, puis s'en va. C'est chaud. C'est la soupe. Oui. Rien n'est cassé. Maman baisse le feu. Le tic devient plus lent. On continue ensemble. Je souffle encore. Bravo, Chouchou. Tu as d'abord respiré. Puis tu as regardé. Tu as fait du bon travail. La soupe mijote tout doucement. Ça sent la carotte et le thym. Je ne suis plus tout surpris. Être surpris, on peut respirer. Puis on cherche à comprendre. La cuillère en bois attend encore. Un rond de buée reste sur la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa aide maman dans la cuisine. Elles préparent une soupe chaude. Soudain, le couvercle saute. Un nuage de vapeur sort. Léa sent son cœur battre vite. Ses yeux s'ouvrent tout grands.
-enfant-f|Je suis surprise.
-maman|D'abord respirer. Ensuite comprendre, avant d'agir.
-narrateur|Léa souffle une grande fois. Elle regarde le faitout.
-narrateur|Je veux comprendre. Elle voit la vapeur.
-narrateur|C'est chaud, c'est la soupe. Rien n'est cassé. Maman baisse le feu. Elles continuent ensemble. Être surpris, on peut respirer.
-narrateur|Puis on cherche à comprendre.</t>
+          <t>narrateur|Des peaux de carotte attendent.
+narrateur|Elles sont orange et un peu humides.
+narrateur|Une cuillère en bois repose.
+narrateur|Le bois sent le chaud.
+narrateur|La vitre de la cuisine est embuée.
+narrateur|La soupe a fait un nuage doux.
+narrateur|Le couvercle fait un petit tic.
+narrateur|Tic, puis encore tic.
+narrateur|Une branche de thym sent fort.
+maman|Tu as entendu, Chouchou ?
+enfant-m|Ça tic.
+maman|C'est le couvercle.
+maman|La soupe est avec nous.
+maman|Tu sens le thym ?
+enfant-m|Ça pique un peu.
+narrateur|En ce moment, Chouchou tient la table.
+narrateur|Le bois est un peu collant.
+maman|Tu me passes le sel ?
+enfant-m|Oui, maman.
+narrateur|Soudain, le couvercle saute.
+narrateur|Un nuage de vapeur sort.
+narrateur|Ça fait un souffle chaud.
+narrateur|Chouchou sent son cœur battre vite.
+narrateur|Ses yeux s'ouvrent tout grands.
+enfant-m|Je suis surpris.
+maman|Tu es surpris.
+maman|Ce n'est pas honteux.
+maman|D'abord respirer.
+maman|Ensuite comprendre, avant d'agir.
+narrateur|Chouchou souffle une grande fois.
+narrateur|Ses épaules redescendent.
+maman|Tu veux comprendre ?
+enfant-m|Je veux comprendre.
+narrateur|Il regarde le faitout, de loin.
+narrateur|La vapeur monte, puis s'en va.
+enfant-m|C'est chaud.
+enfant-m|C'est la soupe.
+maman|Oui.
+maman|Rien n'est cassé.
+narrateur|Maman baisse le feu.
+narrateur|Le tic devient plus lent.
+maman|On continue ensemble.
+enfant-m|Je souffle encore.
+maman|Bravo, Chouchou.
+maman|Tu as d'abord respiré.
+maman|Puis tu as regardé.
+maman|Tu as fait du bon travail.
+narrateur|La soupe mijote tout doucement.
+narrateur|Ça sent la carotte et le thym.
+enfant-m|Je ne suis plus tout surpris.
+maman|Être surpris, on peut respirer.
+maman|Puis on cherche à comprendre.
+narrateur|La cuillère en bois attend encore.
+narrateur|Un rond de buée reste sur la vitre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1405,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léa est surprise. Que fait-elle d'abord ?</t>
+          <t>Chouchou est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léa est surprise. Que fait-elle d'abord ?</t>
+          <t>narrateur|Chouchou est surpris.
+narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a nommé : surpris. Elle a soufflé. Elle a voulu comprendre avant d'agir.</t>
+          <t>La vapeur est plus petite, maintenant. J'ai dit : je suis surpris. Oui. Tu as soufflé. Puis tu as voulu comprendre. Avant d'agir. Bravo, Chouchou. Tu as fait du bon travail. D'abord respirer. Oui. Le faitout fait un bruit tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1738,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a nommé : surpris. Elle a soufflé. Elle a voulu comprendre avant d'agir.</t>
+          <t>narrateur|La vapeur est plus petite, maintenant.
+enfant-m|J'ai dit : je suis surpris.
+maman|Oui.
+maman|Tu as soufflé.
+maman|Puis tu as voulu comprendre.
+maman|Avant d'agir.
+maman|Bravo, Chouchou.
+maman|Tu as fait du bon travail.
+enfant-m|D'abord respirer.
+maman|Oui.
+narrateur|Le faitout fait un bruit tout doux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La soupe mijote tout doucement. Léa pose la cuillère. Maman sourit.</t>
+          <t>La soupe mijote tout doucement. Chouchou pose la cuillère. On reste près de la table ? Oui, maman. Tu as nommé : surpris. Tu as respiré. Tu as regardé. Le thym sent encore. La buée descend un peu sur la vitre. C'était la soupe. Oui. Tu as compris.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1912,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La soupe mijote tout doucement. Léa pose la cuillère. Maman sourit.</t>
+          <t>narrateur|La soupe mijote tout doucement.
+narrateur|Chouchou pose la cuillère.
+maman|On reste près de la table ?
+enfant-m|Oui, maman.
+maman|Tu as nommé : surpris.
+maman|Tu as respiré.
+maman|Tu as regardé.
+narrateur|Le thym sent encore.
+narrateur|La buée descend un peu sur la vitre.
+enfant-m|C'était la soupe.
+maman|Oui.
+maman|Tu as compris.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Chouchou. Tu as fait du bon travail. La soupe continue, tout bas. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2091,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit : je suis surpris.
+enfant-m|J'ai soufflé.
+enfant-m|J'ai compris.
+maman|Bravo, Chouchou.
+maman|Tu as fait du bon travail.
+narrateur|La soupe continue, tout bas.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Des peaux de carotte attendent. Elles sont orange et un peu humides. Une cuillère en bois repose. Le bois sent le chaud. La vitre de la cuisine est embuée. La soupe a fait un nuage doux. Le couvercle fait un petit tic. Tic, puis encore tic. Une branche de thym sent fort. Tu as entendu, Chouchou ? Ça tic. C'est le couvercle. La soupe est avec nous. Tu sens le thym ? Ça pique un peu. En ce moment, Chouchou tient la table. Le bois est un peu collant. Tu me passes le sel ? Oui, maman. Soudain, le couvercle saute. Un nuage de vapeur sort. Ça fait un souffle chaud. Chouchou sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Je suis surpris. Tu es surpris. Ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Chouchou souffle une grande fois. Ses épaules redescendent. Tu veux comprendre ? Je veux comprendre. Il regarde le faitout, de loin. La vapeur monte, puis s'en va. C'est chaud. C'est la soupe. Oui. Rien n'est cassé. Maman baisse le feu. Le tic devient plus lent. On continue ensemble. Je souffle encore. Bravo, Chouchou. Tu as d'abord respiré. Puis tu as regardé. Tu as fait du bon travail. La soupe mijote tout doucement. Ça sent la carotte et le thym. Je ne suis plus tout surpris. Être surpris, on peut respirer. Puis on cherche à comprendre. La cuillère en bois attend encore. Un rond de buée reste sur la vitre.</t>
+          <t>Des peaux de carotte attendent. Elles sont orange et un peu humides. Une cuillère en bois repose. Le bois sent le chaud. La vitre de la cuisine est embuée. La soupe a fait un nuage doux. Le couvercle fait un petit tic. Tic, puis encore tic. Une branche de thym sent fort. Tu as entendu, Chouchou ? Ça tic. C'est le couvercle. La soupe est avec nous. Tu sens le thym ? Ça pique un peu. En ce moment, Chouchou tient la table. Le bois est un peu collant. Tu me passes le sel ? Oui, maman. Soudain, le couvercle saute. Un nuage de vapeur sort. Ça fait un souffle chaud. Chouchou sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Je suis surpris. Tu es surpris. Ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Chouchou souffle une grande fois. Ses épaules redescendent. Tu veux comprendre ? Je veux comprendre. Il regarde le faitout, de loin. La vapeur monte, puis s'en va. C'est chaud. C'est la soupe. Oui. Rien n'est cassé. Maman baisse le feu. Le tic devient plus lent. On continue ensemble. Je souffle encore. Bravo, Chouchou. Tu as d'abord respiré. Puis tu as regardé. La soupe mijote tout doucement. Ça sent la carotte et le thym. Je ne suis plus tout surpris. Être surpris, on peut respirer. Puis on cherche à comprendre. La cuillère en bois attend encore. Un rond de buée reste sur la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa aide maman dans la cuisine. Elles préparent une soupe chaude. Soudain, le couvercle saute. Un nuage de vapeur sort. Léa sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Léa dit : je suis &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. Maman dit : d'abord respirer. Ensuite comprendre, avant d'agir. Léa souffle une grande fois. Elle regarde le faitout. Elle dit : je veux comprendre. Elle voit la vapeur. Elle dit : c'est chaud, c'est la soupe. Rien n'est cassé. Maman baisse le feu. Elles continuent ensemble. Être surpris, on peut respirer. Puis on cherche à comprendre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Des peaux de carotte attendent. Elles sont orange et un peu humides. Une cuillère en bois repose. Le bois sent le chaud. La vitre de la cuisine est embuée. La soupe a fait un nuage doux. Le couvercle fait un petit tic. Tic, puis encore tic. Une branche de thym sent fort. Tu as entendu, Chouchou ? Ça tic. C'est le couvercle. La soupe est avec nous. Tu sens le thym ? Ça pique un peu. En ce moment, Chouchou tient la table. Le bois est un peu collant. Tu me passes le sel ? Oui, maman. Soudain, le couvercle saute. Un nuage de vapeur sort. Ça fait un souffle chaud. Chouchou sent son cœur battre vite. Ses yeux s'ouvrent tout grands. Je suis surpris. Tu es surpris. Ce n'est pas honteux. D'abord respirer. Ensuite comprendre, avant d'agir. Chouchou souffle une grande fois. Ses épaules redescendent. Tu veux comprendre ? Je veux comprendre. Il regarde le faitout, de loin. La vapeur monte, puis s'en va. C'est chaud. C'est la soupe. Oui. Rien n'est cassé. Maman baisse le feu. Le tic devient plus lent. On continue ensemble. Je souffle encore. Bravo, Chouchou. Tu as d'abord respiré. Puis tu as regardé. La soupe mijote tout doucement. Ça sent la carotte et le thym. Je ne suis plus tout surpris. Être surpris, on peut respirer. Puis on cherche à comprendre. La cuillère en bois attend encore. Un rond de buée reste sur la vitre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1370,7 +1370,6 @@
 maman|Bravo, Chouchou.
 maman|Tu as d'abord respiré.
 maman|Puis tu as regardé.
-maman|Tu as fait du bon travail.
 narrateur|La soupe mijote tout doucement.
 narrateur|Ça sent la carotte et le thym.
 enfant-m|Je ne suis plus tout surpris.
@@ -1380,7 +1379,6 @@
 narrateur|Un rond de buée reste sur la vitre.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1410,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa est &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. Que fait-elle d'abord ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou est surpris. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1567,6 @@
 narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>La vapeur est plus petite, maintenant. J'ai dit : je suis surpris. Oui. Tu as soufflé. Puis tu as voulu comprendre. Avant d'agir. Bravo, Chouchou. Tu as fait du bon travail. D'abord respirer. Oui. Le faitout fait un bruit tout doux.</t>
+          <t>La vapeur est plus petite, maintenant. J'ai dit : je suis surpris. Oui. Tu as soufflé. Puis tu as voulu comprendre. Avant d'agir. Bravo, Chouchou. D'abord respirer. Oui. Le faitout fait un bruit tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa a nommé : &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Elle a soufflé. Elle a voulu comprendre avant d'agir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vapeur est plus petite, maintenant. J'ai dit : je suis surpris. Oui. Tu as soufflé. Puis tu as voulu comprendre. Avant d'agir. Bravo, Chouchou. D'abord respirer. Oui. Le faitout fait un bruit tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,13 +1742,11 @@
 maman|Puis tu as voulu comprendre.
 maman|Avant d'agir.
 maman|Bravo, Chouchou.
-maman|Tu as fait du bon travail.
 enfant-m|D'abord respirer.
 maman|Oui.
 narrateur|Le faitout fait un bruit tout doux.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,7 +1776,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La soupe mijote tout doucement. Léa pose la cuillère. Maman sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La soupe mijote tout doucement. Chouchou pose la cuillère. On reste près de la table ? Oui, maman. Tu as nommé : surpris. Tu as respiré. Tu as regardé. Le thym sent encore. La buée descend un peu sur la vitre. C'était la soupe. Oui. Tu as compris.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,7 +1921,6 @@
 maman|Tu as compris.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1951,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Chouchou. Tu as fait du bon travail. La soupe continue, tout bas. L'histoire est finie.</t>
+          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Chouchou. La soupe continue, tout bas.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Chouchou. La soupe continue, tout bas.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,12 +2089,9 @@
 enfant-m|J'ai soufflé.
 enfant-m|J'ai compris.
 maman|Bravo, Chouchou.
-maman|Tu as fait du bon travail.
-narrateur|La soupe continue, tout bas.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La soupe continue, tout bas.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2119,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2155,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
